--- a/activities/lab-05-enhance-powerpoint-with-charts/completed/Lumina-Living-Lab-05-completed.xlsx
+++ b/activities/lab-05-enhance-powerpoint-with-charts/completed/Lumina-Living-Lab-05-completed.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Prompt_Log" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Evidence_Register" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Acceptance_Check" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Chart_Data" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Chart_Summary" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Connected_Workflow" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Scenario" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Prompt_Log" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Evidence_Register" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Acceptance_Check" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Chart_Data" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Chart_Summary" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Acceptance_Check!$A$1:$D$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Chart_Data!$A$1:$H$13</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Chart_Summary!$A$1:$D$7</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Evidence_Register!$A$1:$G$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Prompt_Log!$A$1:$F$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Scenario!$A$1:$H$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Acceptance_Check!$A$1:$D$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Chart_Data!$A$1:$H$13</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Chart_Summary!$A$1:$D$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Evidence_Register!$A$1:$G$5</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Prompt_Log!$A$1:$F$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Scenario!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -33,7 +34,70 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="125">
+  <si>
+    <t xml:space="preserve">Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumina Living Pte Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW-2026 Sustainable Workspace Launch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence visuals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumina-Business-Data.xlsx; Lumina-Management-Report.docx; Lumina-Decision-Deck.pptx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumina-Visual-Evidence.pptx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illustrative comparison only; learner must record actual evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use the Monthly, Channels and HR_Readiness tables to produce three charts. Add them to the Word report and the presentation. Keep PowerPoint chart data editable, show units and source ranges, and reconcile totals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You work for Lumina Living Pte Ltd on SW-2026, the Sustainable Workspace Launch. HR, Marketing, Finance and Operations share one evidence trail. Launch is planned for 1 October 2026; budget SGD 18,000; target 120 qualified enquiries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumina-Business-Data.xlsx; Lumina-Management-Report.docx; Lumina-Decision-Deck.pptx. Use your own reviewed prior-lab files first; scenario/ contains supplied fallback examples.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expectations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save Lumina-Visual-Evidence.pptx. Record source version, verified facts, unresolved questions and reviewer in Lumina-Living-Lab-05.xlsx. Keep projectSW-2026 and action IDsA01–A04 unchanged. Label every output Draft until reviewed; record actual app actions separately.</t>
+  </si>
   <si>
     <t xml:space="preserve">Lab 05: Enhance PowerPoint with Native Charts and Speaker Notes</t>
   </si>
@@ -59,9 +123,6 @@
     <t xml:space="preserve">PowerPoint + Excel + Copilot</t>
   </si>
   <si>
-    <t xml:space="preserve">Goal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Use native PowerPoint charts to strengthen a leadership narrative and prepare a concise delivery.</t>
   </si>
   <si>
@@ -77,9 +138,6 @@
     <t xml:space="preserve">K1 · A1</t>
   </si>
   <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
     <t xml:space="preserve">Completed example</t>
   </si>
   <si>
@@ -104,7 +162,10 @@
     <t xml:space="preserve">Enhance PowerPoint with Native Charts and Speaker Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Improve the attached leadership deck using the workbook as the only numerical source. Recommend where a trend chart, contribution chart and variance chart add decision value. For each, state the takeaway title, the correct chart type, the data range and one caveat. Then draft speaker notes of 60-90 words per chart slide.</t>
+    <t xml:space="preserve">Goal: Use the Monthly, Channels and HR_Readiness tables to produce three charts. Add them to the Word report and the presentation. Keep PowerPoint chart data editable, show units and source ranges, and reconcile totals.
+Context: You work for Lumina Living Pte Ltd on SW-2026, the Sustainable Workspace Launch. HR, Marketing, Finance and Operations share one evidence trail. Launch is planned for 1 October 2026; budget SGD 18,000; target 120 qualified enquiries.
+Source: Lumina-Business-Data.xlsx; Lumina-Management-Report.docx; Lumina-Decision-Deck.pptx. Use your own reviewed prior-lab files first; scenario/ contains supplied fallback examples.
+Expectations: Save Lumina-Visual-Evidence.pptx. Record source version, verified facts, unresolved questions and reviewer in Lumina-Living-Lab-05.xlsx. Keep projectSW-2026 and action IDsA01–A04 unchanged. Label every output Draft until reviewed; record actual app actions separately.</t>
   </si>
   <si>
     <t xml:space="preserve">Attached lab files only</t>
@@ -122,9 +183,6 @@
     <t xml:space="preserve">Artifact</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check</t>
   </si>
   <si>
@@ -329,31 +387,31 @@
     <t xml:space="preserve">Month</t>
   </si>
   <si>
-    <t xml:space="preserve">Actual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec</t>
+    <t xml:space="preserve">Revenue_SGD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost_SGD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin_SGD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jun</t>
   </si>
 </sst>
 </file>
@@ -364,7 +422,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,6 +444,20 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -501,16 +573,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -518,19 +602,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -542,7 +626,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -700,7 +784,7 @@
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Campaign performance versus target</a:t>
+              <a:t>Historical revenue and cost by month</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -727,7 +811,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Actual</c:v>
+                  <c:v>Revenue_SGD</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -748,23 +832,27 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -787,22 +875,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Jul</c:v>
+                  <c:v>Jan</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Aug</c:v>
+                  <c:v>Feb</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Sep</c:v>
+                  <c:v>Mar</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Oct</c:v>
+                  <c:v>Apr</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Nov</c:v>
+                  <c:v>May</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Dec</c:v>
+                  <c:v>Jun</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -814,22 +902,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>72</c:v>
+                  <c:v>90150</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>79</c:v>
+                  <c:v>145565</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>86</c:v>
+                  <c:v>130880</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>93</c:v>
+                  <c:v>189070</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100</c:v>
+                  <c:v>159920</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>107</c:v>
+                  <c:v>217705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -845,7 +933,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Target</c:v>
+                  <c:v>Cost_SGD</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -866,23 +954,27 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -905,22 +997,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Jul</c:v>
+                  <c:v>Jan</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Aug</c:v>
+                  <c:v>Feb</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Sep</c:v>
+                  <c:v>Mar</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Oct</c:v>
+                  <c:v>Apr</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Nov</c:v>
+                  <c:v>May</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Dec</c:v>
+                  <c:v>Jun</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -932,22 +1024,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>78</c:v>
+                  <c:v>45976.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>83</c:v>
+                  <c:v>80788.61</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>88</c:v>
+                  <c:v>78528</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>93</c:v>
+                  <c:v>96425.7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>98</c:v>
+                  <c:v>88755.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>103</c:v>
+                  <c:v>130623</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -962,17 +1054,17 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="4662075"/>
-        <c:axId val="73722843"/>
+        <c:axId val="82638086"/>
+        <c:axId val="92746728"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="4662075"/>
+        <c:axId val="82638086"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -999,7 +1091,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73722843"/>
+        <c:crossAx val="92746728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1007,7 +1099,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73722843"/>
+        <c:axId val="92746728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1023,7 +1115,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1050,7 +1142,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4662075"/>
+        <c:crossAx val="82638086"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1352,9 +1444,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>507600</xdr:colOff>
+      <xdr:colOff>507240</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>32400</xdr:rowOff>
+      <xdr:rowOff>32040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1363,7 +1455,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3712680" y="190440"/>
-        <a:ext cx="5399640" cy="2699640"/>
+        <a:ext cx="5399280" cy="2699280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1601,144 +1693,255 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="110"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="3" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="3" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="B10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H10"/>
@@ -1757,7 +1960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1765,175 +1968,54 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="3" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="3" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>26</v>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-  <tableParts>
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="7"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G5"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1953,40 +2035,161 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="3" width="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+  <tableParts>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="3" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2002,7 +2205,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2010,351 +2213,351 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="6" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="9" t="n">
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="12" t="n">
         <v>46254</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="10" t="n">
+      <c r="E2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="13" t="n">
         <v>46259</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="10" t="n">
+      <c r="E3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="13" t="n">
         <v>46264</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="10" t="n">
+      <c r="E4" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="13" t="n">
         <v>46269</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="E5" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="D6" s="13" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>46284</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="F8" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>46279</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="G8" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="D11" s="13" t="n">
+        <v>46299</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>46284</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>46289</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="F12" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>46294</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="F13" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>46299</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>46304</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>46309</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>66</v>
+      <c r="G13" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2373,7 +2576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2381,111 +2584,111 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="3" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="D2" s="3" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>90150</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>45976.5</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <f aca="false">B2-C2</f>
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>79</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>83</v>
-      </c>
-      <c r="D3" s="7" t="n">
+        <v>44173.5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>145565</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>80788.61</v>
+      </c>
+      <c r="D3" s="10" t="n">
         <f aca="false">B3-C3</f>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>86</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>88</v>
-      </c>
-      <c r="D4" s="7" t="n">
+        <v>64776.39</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>130880</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>78528</v>
+      </c>
+      <c r="D4" s="10" t="n">
         <f aca="false">B4-C4</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="D5" s="7" t="n">
+        <v>52352</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>189070</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>96425.7</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <f aca="false">B5-C5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="D6" s="7" t="n">
+        <v>92644.3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>159920</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>88755.6</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <f aca="false">B6-C6</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>103</v>
-      </c>
-      <c r="D7" s="7" t="n">
+        <v>71164.4</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>217705</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>130623</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <f aca="false">B7-C7</f>
-        <v>4</v>
+        <v>87082</v>
       </c>
     </row>
   </sheetData>
